--- a/output/pdf_financials_xlsx/INVR.xlsx
+++ b/output/pdf_financials_xlsx/INVR.xlsx
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.158521</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.374292</v>
       </c>
     </row>
     <row r="93">
@@ -3800,7 +3800,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>1.158521</v>
       </c>

--- a/output/pdf_financials_xlsx/INVR.xlsx
+++ b/output/pdf_financials_xlsx/INVR.xlsx
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.044005</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.056596</v>
       </c>
     </row>
     <row r="35">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.044005</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.056596</v>
       </c>
     </row>
     <row r="37">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.026992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">

--- a/output/pdf_financials_xlsx/INVR.xlsx
+++ b/output/pdf_financials_xlsx/INVR.xlsx
@@ -5439,7 +5439,11 @@
           <t>Loan interest revenue 6</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.20163</v>
       </c>
